--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-19T09:04:56+00:00</t>
+    <t>2024-02-19T13:34:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-19T13:34:28+00:00</t>
+    <t>2024-02-19T13:42:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-19T13:42:29+00:00</t>
+    <t>2024-03-04T16:55:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-04T16:55:03+00:00</t>
+    <t>2024-03-05T15:34:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-05T15:34:40+00:00</t>
+    <t>2024-03-06T10:45:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-06T10:45:14+00:00</t>
+    <t>2024-03-07T10:27:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-07T10:27:01+00:00</t>
+    <t>2024-03-12T12:54:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T12:54:34+00:00</t>
+    <t>2024-03-12T13:20:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T13:20:54+00:00</t>
+    <t>2024-03-12T13:39:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T13:39:01+00:00</t>
+    <t>2024-03-12T13:58:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T13:58:30+00:00</t>
+    <t>2024-03-12T14:02:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T14:02:45+00:00</t>
+    <t>2024-03-12T14:08:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T14:08:02+00:00</t>
+    <t>2024-03-12T14:13:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T14:13:18+00:00</t>
+    <t>2024-03-12T14:29:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T14:29:58+00:00</t>
+    <t>2024-03-12T16:57:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T16:57:02+00:00</t>
+    <t>2024-03-12T17:28:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T17:28:16+00:00</t>
+    <t>2024-03-13T08:21:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,13 +57,13 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-13T08:21:45+00:00</t>
+    <t>2024-03-13T15:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>ANS</t>
+    <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris</t>
   </si>
   <si>
     <t>Contact</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-13T15:21:15+00:00</t>
+    <t>2024-03-13T15:40:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-13T15:40:01+00:00</t>
+    <t>2024-03-15T14:37:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-02T13:53:07+00:00</t>
+    <t>2024-04-02T14:01:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0-ballot-4</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-02T14:01:28+00:00</t>
+    <t>2024-04-03T13:55:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-08T12:41:20+00:00</t>
+    <t>2024-04-08T12:53:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-08T12:53:48+00:00</t>
+    <t>2024-04-09T07:46:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -322,9 +322,6 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>Extension.extension:serialNumber</t>
   </si>
   <si>
@@ -370,6 +367,9 @@
   </si>
   <si>
     <t>Extension.url</t>
+  </si>
+  <si>
+    <t>N/A</t>
   </si>
   <si>
     <t>Extension.extension:serialNumber.value[x]</t>
@@ -499,8 +499,8 @@
     <t>Period.start</t>
   </si>
   <si>
-    <t>ele-1
-per-1</t>
+    <t xml:space="preserve">per-1
+</t>
   </si>
   <si>
     <t>./low</t>
@@ -1375,24 +1375,24 @@
         <v>79</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AJ4" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AK4" t="s" s="2">
-        <v>100</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B5" t="s" s="2">
         <v>90</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D5" t="s" s="2">
         <v>77</v>
@@ -1417,10 +1417,10 @@
         <v>92</v>
       </c>
       <c r="L5" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="M5" t="s" s="2">
         <v>103</v>
-      </c>
-      <c r="M5" t="s" s="2">
-        <v>104</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1480,7 +1480,7 @@
         <v>79</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AJ5" t="s" s="2">
         <v>82</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="B6" t="s" s="2">
         <v>105</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>106</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1594,10 +1594,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="B7" t="s" s="2">
         <v>107</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>108</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1626,7 +1626,7 @@
         <v>30</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1686,7 +1686,7 @@
         <v>79</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AJ7" t="s" s="2">
         <v>82</v>
@@ -1697,10 +1697,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="B8" t="s" s="2">
         <v>109</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>110</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1723,16 +1723,16 @@
         <v>77</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="M8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>113</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>114</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="S8" t="s" s="2">
         <v>77</v>
@@ -1782,22 +1782,22 @@
         <v>77</v>
       </c>
       <c r="AF8" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AG8" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AH8" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK8" t="s" s="2">
         <v>115</v>
-      </c>
-      <c r="AG8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AH8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK8" t="s" s="2">
-        <v>100</v>
       </c>
     </row>
     <row r="9">
@@ -1894,13 +1894,13 @@
         <v>84</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AJ9" t="s" s="2">
         <v>121</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>100</v>
+        <v>115</v>
       </c>
     </row>
     <row r="10">
@@ -1939,7 +1939,7 @@
         <v>124</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1999,7 +1999,7 @@
         <v>79</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>82</v>
@@ -2013,7 +2013,7 @@
         <v>125</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2116,7 +2116,7 @@
         <v>126</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2145,7 +2145,7 @@
         <v>30</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2205,7 +2205,7 @@
         <v>79</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>82</v>
@@ -2219,7 +2219,7 @@
         <v>127</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2242,16 +2242,16 @@
         <v>77</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="M13" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>113</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>114</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2301,22 +2301,22 @@
         <v>77</v>
       </c>
       <c r="AF13" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AG13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AH13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK13" t="s" s="2">
         <v>115</v>
-      </c>
-      <c r="AG13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AH13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK13" t="s" s="2">
-        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -2413,13 +2413,13 @@
         <v>84</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>121</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>100</v>
+        <v>115</v>
       </c>
     </row>
     <row r="15">
@@ -2458,7 +2458,7 @@
         <v>131</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2518,7 +2518,7 @@
         <v>79</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AJ15" t="s" s="2">
         <v>82</v>
@@ -2532,7 +2532,7 @@
         <v>132</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2635,7 +2635,7 @@
         <v>133</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2664,7 +2664,7 @@
         <v>30</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2724,7 +2724,7 @@
         <v>79</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AJ17" t="s" s="2">
         <v>82</v>
@@ -2738,7 +2738,7 @@
         <v>134</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2761,16 +2761,16 @@
         <v>77</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>113</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>114</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -2820,22 +2820,22 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AG18" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AH18" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK18" t="s" s="2">
         <v>115</v>
-      </c>
-      <c r="AG18" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AH18" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK18" t="s" s="2">
-        <v>100</v>
       </c>
     </row>
     <row r="19">
@@ -2932,13 +2932,13 @@
         <v>84</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>121</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>100</v>
+        <v>115</v>
       </c>
     </row>
     <row r="20">
@@ -2977,7 +2977,7 @@
         <v>138</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3037,7 +3037,7 @@
         <v>79</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>82</v>
@@ -3051,7 +3051,7 @@
         <v>139</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3154,7 +3154,7 @@
         <v>140</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3183,7 +3183,7 @@
         <v>30</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3243,7 +3243,7 @@
         <v>79</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>82</v>
@@ -3257,7 +3257,7 @@
         <v>141</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3280,16 +3280,16 @@
         <v>77</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>113</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>114</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -3339,22 +3339,22 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AG23" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AH23" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK23" t="s" s="2">
         <v>115</v>
-      </c>
-      <c r="AG23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AH23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK23" t="s" s="2">
-        <v>100</v>
       </c>
     </row>
     <row r="24">
@@ -3451,13 +3451,13 @@
         <v>84</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>121</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>100</v>
+        <v>115</v>
       </c>
     </row>
     <row r="25">
@@ -3659,13 +3659,13 @@
         <v>79</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>100</v>
+        <v>89</v>
       </c>
     </row>
     <row r="27">
@@ -3916,7 +3916,7 @@
         <v>168</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -3976,7 +3976,7 @@
         <v>79</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>82</v>
@@ -3990,7 +3990,7 @@
         <v>169</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4093,7 +4093,7 @@
         <v>170</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4122,7 +4122,7 @@
         <v>30</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4182,7 +4182,7 @@
         <v>79</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>82</v>
@@ -4196,7 +4196,7 @@
         <v>171</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4219,16 +4219,16 @@
         <v>77</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>113</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>114</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -4278,22 +4278,22 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AG32" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AH32" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK32" t="s" s="2">
         <v>115</v>
-      </c>
-      <c r="AG32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AH32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK32" t="s" s="2">
-        <v>100</v>
       </c>
     </row>
     <row r="33">
@@ -4390,13 +4390,13 @@
         <v>84</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>121</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>100</v>
+        <v>115</v>
       </c>
     </row>
     <row r="34">
@@ -4435,7 +4435,7 @@
         <v>175</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4495,7 +4495,7 @@
         <v>79</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>82</v>
@@ -4509,7 +4509,7 @@
         <v>176</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4612,7 +4612,7 @@
         <v>177</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4641,7 +4641,7 @@
         <v>30</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4701,7 +4701,7 @@
         <v>79</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>82</v>
@@ -4715,7 +4715,7 @@
         <v>178</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4738,16 +4738,16 @@
         <v>77</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>113</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>114</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -4797,22 +4797,22 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AG37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AH37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK37" t="s" s="2">
         <v>115</v>
-      </c>
-      <c r="AG37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AH37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK37" t="s" s="2">
-        <v>100</v>
       </c>
     </row>
     <row r="38">
@@ -4909,13 +4909,13 @@
         <v>84</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>121</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>100</v>
+        <v>115</v>
       </c>
     </row>
     <row r="39">
@@ -4954,7 +4954,7 @@
         <v>182</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5014,7 +5014,7 @@
         <v>79</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>82</v>
@@ -5028,7 +5028,7 @@
         <v>183</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5131,7 +5131,7 @@
         <v>184</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5160,7 +5160,7 @@
         <v>30</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5220,7 +5220,7 @@
         <v>79</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>82</v>
@@ -5234,7 +5234,7 @@
         <v>185</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5257,16 +5257,16 @@
         <v>77</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>113</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>114</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -5316,22 +5316,22 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AG42" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AH42" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK42" t="s" s="2">
         <v>115</v>
-      </c>
-      <c r="AG42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AH42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK42" t="s" s="2">
-        <v>100</v>
       </c>
     </row>
     <row r="43">
@@ -5428,21 +5428,21 @@
         <v>84</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>121</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>100</v>
+        <v>115</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -5465,16 +5465,16 @@
         <v>77</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="M44" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>113</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>114</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -5524,22 +5524,22 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK44" t="s" s="2">
         <v>115</v>
-      </c>
-      <c r="AG44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AH44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK44" t="s" s="2">
-        <v>100</v>
       </c>
     </row>
     <row r="45">
@@ -5636,13 +5636,13 @@
         <v>84</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>121</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>100</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-09T07:46:55+00:00</t>
+    <t>2024-04-10T12:18:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -322,6 +322,9 @@
     <t>Element.extension</t>
   </si>
   <si>
+    <t>N/A</t>
+  </si>
+  <si>
     <t>Extension.extension:serialNumber</t>
   </si>
   <si>
@@ -367,9 +370,6 @@
   </si>
   <si>
     <t>Extension.url</t>
-  </si>
-  <si>
-    <t>N/A</t>
   </si>
   <si>
     <t>Extension.extension:serialNumber.value[x]</t>
@@ -499,8 +499,8 @@
     <t>Period.start</t>
   </si>
   <si>
-    <t xml:space="preserve">per-1
-</t>
+    <t>ele-1
+per-1</t>
   </si>
   <si>
     <t>./low</t>
@@ -1375,24 +1375,24 @@
         <v>79</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AJ4" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AK4" t="s" s="2">
-        <v>89</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B5" t="s" s="2">
         <v>90</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D5" t="s" s="2">
         <v>77</v>
@@ -1417,10 +1417,10 @@
         <v>92</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1480,7 +1480,7 @@
         <v>79</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AJ5" t="s" s="2">
         <v>82</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1594,10 +1594,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1626,7 +1626,7 @@
         <v>30</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1686,7 +1686,7 @@
         <v>79</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AJ7" t="s" s="2">
         <v>82</v>
@@ -1697,10 +1697,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1723,16 +1723,16 @@
         <v>77</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="S8" t="s" s="2">
         <v>77</v>
@@ -1782,7 +1782,7 @@
         <v>77</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>84</v>
@@ -1797,7 +1797,7 @@
         <v>77</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9">
@@ -1894,13 +1894,13 @@
         <v>84</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AJ9" t="s" s="2">
         <v>121</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10">
@@ -1939,7 +1939,7 @@
         <v>124</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1999,7 +1999,7 @@
         <v>79</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>82</v>
@@ -2013,7 +2013,7 @@
         <v>125</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2116,7 +2116,7 @@
         <v>126</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2145,7 +2145,7 @@
         <v>30</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2205,7 +2205,7 @@
         <v>79</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>82</v>
@@ -2219,7 +2219,7 @@
         <v>127</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2242,16 +2242,16 @@
         <v>77</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2301,7 +2301,7 @@
         <v>77</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>84</v>
@@ -2316,7 +2316,7 @@
         <v>77</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -2413,13 +2413,13 @@
         <v>84</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>121</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -2458,7 +2458,7 @@
         <v>131</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2518,7 +2518,7 @@
         <v>79</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AJ15" t="s" s="2">
         <v>82</v>
@@ -2532,7 +2532,7 @@
         <v>132</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2635,7 +2635,7 @@
         <v>133</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2664,7 +2664,7 @@
         <v>30</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2724,7 +2724,7 @@
         <v>79</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AJ17" t="s" s="2">
         <v>82</v>
@@ -2738,7 +2738,7 @@
         <v>134</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2761,16 +2761,16 @@
         <v>77</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -2820,7 +2820,7 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>84</v>
@@ -2835,7 +2835,7 @@
         <v>77</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19">
@@ -2932,13 +2932,13 @@
         <v>84</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>121</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20">
@@ -2977,7 +2977,7 @@
         <v>138</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3037,7 +3037,7 @@
         <v>79</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>82</v>
@@ -3051,7 +3051,7 @@
         <v>139</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3154,7 +3154,7 @@
         <v>140</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3183,7 +3183,7 @@
         <v>30</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3243,7 +3243,7 @@
         <v>79</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>82</v>
@@ -3257,7 +3257,7 @@
         <v>141</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3280,16 +3280,16 @@
         <v>77</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -3339,7 +3339,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>84</v>
@@ -3354,7 +3354,7 @@
         <v>77</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24">
@@ -3451,13 +3451,13 @@
         <v>84</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>121</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25">
@@ -3659,13 +3659,13 @@
         <v>79</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>89</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27">
@@ -3916,7 +3916,7 @@
         <v>168</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -3976,7 +3976,7 @@
         <v>79</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>82</v>
@@ -3990,7 +3990,7 @@
         <v>169</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4093,7 +4093,7 @@
         <v>170</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4122,7 +4122,7 @@
         <v>30</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4182,7 +4182,7 @@
         <v>79</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>82</v>
@@ -4196,7 +4196,7 @@
         <v>171</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4219,16 +4219,16 @@
         <v>77</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -4278,7 +4278,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>84</v>
@@ -4293,7 +4293,7 @@
         <v>77</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
     <row r="33">
@@ -4390,13 +4390,13 @@
         <v>84</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>121</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
     <row r="34">
@@ -4435,7 +4435,7 @@
         <v>175</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4495,7 +4495,7 @@
         <v>79</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>82</v>
@@ -4509,7 +4509,7 @@
         <v>176</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4612,7 +4612,7 @@
         <v>177</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4641,7 +4641,7 @@
         <v>30</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4701,7 +4701,7 @@
         <v>79</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>82</v>
@@ -4715,7 +4715,7 @@
         <v>178</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4738,16 +4738,16 @@
         <v>77</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -4797,7 +4797,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>84</v>
@@ -4812,7 +4812,7 @@
         <v>77</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
     <row r="38">
@@ -4909,13 +4909,13 @@
         <v>84</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>121</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
     <row r="39">
@@ -4954,7 +4954,7 @@
         <v>182</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5014,7 +5014,7 @@
         <v>79</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>82</v>
@@ -5028,7 +5028,7 @@
         <v>183</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5131,7 +5131,7 @@
         <v>184</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5160,7 +5160,7 @@
         <v>30</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5220,7 +5220,7 @@
         <v>79</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>82</v>
@@ -5234,7 +5234,7 @@
         <v>185</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5257,16 +5257,16 @@
         <v>77</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -5316,7 +5316,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>84</v>
@@ -5331,7 +5331,7 @@
         <v>77</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
     <row r="43">
@@ -5428,21 +5428,21 @@
         <v>84</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>121</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -5465,16 +5465,16 @@
         <v>77</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -5524,7 +5524,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>84</v>
@@ -5539,7 +5539,7 @@
         <v>77</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
     <row r="45">
@@ -5636,13 +5636,13 @@
         <v>84</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>121</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T12:18:24+00:00</t>
+    <t>2024-04-10T12:37:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -322,9 +322,6 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>Extension.extension:serialNumber</t>
   </si>
   <si>
@@ -370,6 +367,9 @@
   </si>
   <si>
     <t>Extension.url</t>
+  </si>
+  <si>
+    <t>N/A</t>
   </si>
   <si>
     <t>Extension.extension:serialNumber.value[x]</t>
@@ -499,8 +499,8 @@
     <t>Period.start</t>
   </si>
   <si>
-    <t>ele-1
-per-1</t>
+    <t xml:space="preserve">per-1
+</t>
   </si>
   <si>
     <t>./low</t>
@@ -1375,24 +1375,24 @@
         <v>79</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AJ4" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AK4" t="s" s="2">
-        <v>100</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B5" t="s" s="2">
         <v>90</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D5" t="s" s="2">
         <v>77</v>
@@ -1417,10 +1417,10 @@
         <v>92</v>
       </c>
       <c r="L5" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="M5" t="s" s="2">
         <v>103</v>
-      </c>
-      <c r="M5" t="s" s="2">
-        <v>104</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1480,7 +1480,7 @@
         <v>79</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AJ5" t="s" s="2">
         <v>82</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="B6" t="s" s="2">
         <v>105</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>106</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1594,10 +1594,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="B7" t="s" s="2">
         <v>107</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>108</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1626,7 +1626,7 @@
         <v>30</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1686,7 +1686,7 @@
         <v>79</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AJ7" t="s" s="2">
         <v>82</v>
@@ -1697,10 +1697,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="B8" t="s" s="2">
         <v>109</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>110</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1723,16 +1723,16 @@
         <v>77</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="M8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>113</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>114</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="S8" t="s" s="2">
         <v>77</v>
@@ -1782,22 +1782,22 @@
         <v>77</v>
       </c>
       <c r="AF8" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AG8" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AH8" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK8" t="s" s="2">
         <v>115</v>
-      </c>
-      <c r="AG8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AH8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK8" t="s" s="2">
-        <v>100</v>
       </c>
     </row>
     <row r="9">
@@ -1894,13 +1894,13 @@
         <v>84</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AJ9" t="s" s="2">
         <v>121</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>100</v>
+        <v>115</v>
       </c>
     </row>
     <row r="10">
@@ -1939,7 +1939,7 @@
         <v>124</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1999,7 +1999,7 @@
         <v>79</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>82</v>
@@ -2013,7 +2013,7 @@
         <v>125</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2116,7 +2116,7 @@
         <v>126</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2145,7 +2145,7 @@
         <v>30</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2205,7 +2205,7 @@
         <v>79</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>82</v>
@@ -2219,7 +2219,7 @@
         <v>127</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2242,16 +2242,16 @@
         <v>77</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="M13" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>113</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>114</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2301,22 +2301,22 @@
         <v>77</v>
       </c>
       <c r="AF13" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AG13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AH13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK13" t="s" s="2">
         <v>115</v>
-      </c>
-      <c r="AG13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AH13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK13" t="s" s="2">
-        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -2413,13 +2413,13 @@
         <v>84</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>121</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>100</v>
+        <v>115</v>
       </c>
     </row>
     <row r="15">
@@ -2458,7 +2458,7 @@
         <v>131</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2518,7 +2518,7 @@
         <v>79</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AJ15" t="s" s="2">
         <v>82</v>
@@ -2532,7 +2532,7 @@
         <v>132</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2635,7 +2635,7 @@
         <v>133</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2664,7 +2664,7 @@
         <v>30</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2724,7 +2724,7 @@
         <v>79</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AJ17" t="s" s="2">
         <v>82</v>
@@ -2738,7 +2738,7 @@
         <v>134</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2761,16 +2761,16 @@
         <v>77</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>113</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>114</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -2820,22 +2820,22 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AG18" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AH18" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK18" t="s" s="2">
         <v>115</v>
-      </c>
-      <c r="AG18" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AH18" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK18" t="s" s="2">
-        <v>100</v>
       </c>
     </row>
     <row r="19">
@@ -2932,13 +2932,13 @@
         <v>84</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>121</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>100</v>
+        <v>115</v>
       </c>
     </row>
     <row r="20">
@@ -2977,7 +2977,7 @@
         <v>138</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3037,7 +3037,7 @@
         <v>79</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>82</v>
@@ -3051,7 +3051,7 @@
         <v>139</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3154,7 +3154,7 @@
         <v>140</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3183,7 +3183,7 @@
         <v>30</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3243,7 +3243,7 @@
         <v>79</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>82</v>
@@ -3257,7 +3257,7 @@
         <v>141</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3280,16 +3280,16 @@
         <v>77</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>113</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>114</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -3339,22 +3339,22 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AG23" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AH23" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK23" t="s" s="2">
         <v>115</v>
-      </c>
-      <c r="AG23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AH23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK23" t="s" s="2">
-        <v>100</v>
       </c>
     </row>
     <row r="24">
@@ -3451,13 +3451,13 @@
         <v>84</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>121</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>100</v>
+        <v>115</v>
       </c>
     </row>
     <row r="25">
@@ -3659,13 +3659,13 @@
         <v>79</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>100</v>
+        <v>89</v>
       </c>
     </row>
     <row r="27">
@@ -3916,7 +3916,7 @@
         <v>168</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -3976,7 +3976,7 @@
         <v>79</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>82</v>
@@ -3990,7 +3990,7 @@
         <v>169</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4093,7 +4093,7 @@
         <v>170</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4122,7 +4122,7 @@
         <v>30</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4182,7 +4182,7 @@
         <v>79</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>82</v>
@@ -4196,7 +4196,7 @@
         <v>171</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4219,16 +4219,16 @@
         <v>77</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>113</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>114</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -4278,22 +4278,22 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AG32" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AH32" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK32" t="s" s="2">
         <v>115</v>
-      </c>
-      <c r="AG32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AH32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK32" t="s" s="2">
-        <v>100</v>
       </c>
     </row>
     <row r="33">
@@ -4390,13 +4390,13 @@
         <v>84</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>121</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>100</v>
+        <v>115</v>
       </c>
     </row>
     <row r="34">
@@ -4435,7 +4435,7 @@
         <v>175</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4495,7 +4495,7 @@
         <v>79</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>82</v>
@@ -4509,7 +4509,7 @@
         <v>176</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4612,7 +4612,7 @@
         <v>177</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4641,7 +4641,7 @@
         <v>30</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4701,7 +4701,7 @@
         <v>79</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>82</v>
@@ -4715,7 +4715,7 @@
         <v>178</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4738,16 +4738,16 @@
         <v>77</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>113</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>114</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -4797,22 +4797,22 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AG37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AH37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK37" t="s" s="2">
         <v>115</v>
-      </c>
-      <c r="AG37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AH37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK37" t="s" s="2">
-        <v>100</v>
       </c>
     </row>
     <row r="38">
@@ -4909,13 +4909,13 @@
         <v>84</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>121</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>100</v>
+        <v>115</v>
       </c>
     </row>
     <row r="39">
@@ -4954,7 +4954,7 @@
         <v>182</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5014,7 +5014,7 @@
         <v>79</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>82</v>
@@ -5028,7 +5028,7 @@
         <v>183</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5131,7 +5131,7 @@
         <v>184</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5160,7 +5160,7 @@
         <v>30</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5220,7 +5220,7 @@
         <v>79</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>82</v>
@@ -5234,7 +5234,7 @@
         <v>185</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5257,16 +5257,16 @@
         <v>77</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>113</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>114</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -5316,22 +5316,22 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AG42" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AH42" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK42" t="s" s="2">
         <v>115</v>
-      </c>
-      <c r="AG42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AH42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK42" t="s" s="2">
-        <v>100</v>
       </c>
     </row>
     <row r="43">
@@ -5428,21 +5428,21 @@
         <v>84</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>121</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>100</v>
+        <v>115</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -5465,16 +5465,16 @@
         <v>77</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="M44" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>113</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>114</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -5524,22 +5524,22 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK44" t="s" s="2">
         <v>115</v>
-      </c>
-      <c r="AG44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AH44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK44" t="s" s="2">
-        <v>100</v>
       </c>
     </row>
     <row r="45">
@@ -5636,13 +5636,13 @@
         <v>84</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>121</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>100</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:21:45+00:00</t>
+    <t>2024-04-18T13:43:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-18T13:43:00+00:00</t>
+    <t>2024-04-25T11:33:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -322,6 +322,9 @@
     <t>Element.extension</t>
   </si>
   <si>
+    <t>N/A</t>
+  </si>
+  <si>
     <t>Extension.extension:serialNumber</t>
   </si>
   <si>
@@ -367,9 +370,6 @@
   </si>
   <si>
     <t>Extension.url</t>
-  </si>
-  <si>
-    <t>N/A</t>
   </si>
   <si>
     <t>Extension.extension:serialNumber.value[x]</t>
@@ -499,8 +499,8 @@
     <t>Period.start</t>
   </si>
   <si>
-    <t xml:space="preserve">per-1
-</t>
+    <t>ele-1
+per-1</t>
   </si>
   <si>
     <t>./low</t>
@@ -1375,24 +1375,24 @@
         <v>79</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AJ4" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AK4" t="s" s="2">
-        <v>89</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B5" t="s" s="2">
         <v>90</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D5" t="s" s="2">
         <v>77</v>
@@ -1417,10 +1417,10 @@
         <v>92</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1480,7 +1480,7 @@
         <v>79</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AJ5" t="s" s="2">
         <v>82</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1594,10 +1594,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1626,7 +1626,7 @@
         <v>30</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1686,7 +1686,7 @@
         <v>79</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AJ7" t="s" s="2">
         <v>82</v>
@@ -1697,10 +1697,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1723,16 +1723,16 @@
         <v>77</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="S8" t="s" s="2">
         <v>77</v>
@@ -1782,7 +1782,7 @@
         <v>77</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>84</v>
@@ -1797,7 +1797,7 @@
         <v>77</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9">
@@ -1894,13 +1894,13 @@
         <v>84</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AJ9" t="s" s="2">
         <v>121</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10">
@@ -1939,7 +1939,7 @@
         <v>124</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1999,7 +1999,7 @@
         <v>79</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>82</v>
@@ -2013,7 +2013,7 @@
         <v>125</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2116,7 +2116,7 @@
         <v>126</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2145,7 +2145,7 @@
         <v>30</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2205,7 +2205,7 @@
         <v>79</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>82</v>
@@ -2219,7 +2219,7 @@
         <v>127</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2242,16 +2242,16 @@
         <v>77</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2301,7 +2301,7 @@
         <v>77</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>84</v>
@@ -2316,7 +2316,7 @@
         <v>77</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -2413,13 +2413,13 @@
         <v>84</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>121</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -2458,7 +2458,7 @@
         <v>131</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2518,7 +2518,7 @@
         <v>79</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AJ15" t="s" s="2">
         <v>82</v>
@@ -2532,7 +2532,7 @@
         <v>132</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2635,7 +2635,7 @@
         <v>133</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2664,7 +2664,7 @@
         <v>30</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2724,7 +2724,7 @@
         <v>79</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AJ17" t="s" s="2">
         <v>82</v>
@@ -2738,7 +2738,7 @@
         <v>134</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2761,16 +2761,16 @@
         <v>77</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -2820,7 +2820,7 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>84</v>
@@ -2835,7 +2835,7 @@
         <v>77</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19">
@@ -2932,13 +2932,13 @@
         <v>84</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>121</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20">
@@ -2977,7 +2977,7 @@
         <v>138</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3037,7 +3037,7 @@
         <v>79</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>82</v>
@@ -3051,7 +3051,7 @@
         <v>139</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3154,7 +3154,7 @@
         <v>140</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3183,7 +3183,7 @@
         <v>30</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3243,7 +3243,7 @@
         <v>79</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>82</v>
@@ -3257,7 +3257,7 @@
         <v>141</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3280,16 +3280,16 @@
         <v>77</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -3339,7 +3339,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>84</v>
@@ -3354,7 +3354,7 @@
         <v>77</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24">
@@ -3451,13 +3451,13 @@
         <v>84</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>121</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25">
@@ -3659,13 +3659,13 @@
         <v>79</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>89</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27">
@@ -3916,7 +3916,7 @@
         <v>168</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -3976,7 +3976,7 @@
         <v>79</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>82</v>
@@ -3990,7 +3990,7 @@
         <v>169</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4093,7 +4093,7 @@
         <v>170</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4122,7 +4122,7 @@
         <v>30</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4182,7 +4182,7 @@
         <v>79</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>82</v>
@@ -4196,7 +4196,7 @@
         <v>171</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4219,16 +4219,16 @@
         <v>77</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -4278,7 +4278,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>84</v>
@@ -4293,7 +4293,7 @@
         <v>77</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
     <row r="33">
@@ -4390,13 +4390,13 @@
         <v>84</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>121</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
     <row r="34">
@@ -4435,7 +4435,7 @@
         <v>175</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4495,7 +4495,7 @@
         <v>79</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>82</v>
@@ -4509,7 +4509,7 @@
         <v>176</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4612,7 +4612,7 @@
         <v>177</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4641,7 +4641,7 @@
         <v>30</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4701,7 +4701,7 @@
         <v>79</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>82</v>
@@ -4715,7 +4715,7 @@
         <v>178</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4738,16 +4738,16 @@
         <v>77</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -4797,7 +4797,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>84</v>
@@ -4812,7 +4812,7 @@
         <v>77</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
     <row r="38">
@@ -4909,13 +4909,13 @@
         <v>84</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>121</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
     <row r="39">
@@ -4954,7 +4954,7 @@
         <v>182</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5014,7 +5014,7 @@
         <v>79</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>82</v>
@@ -5028,7 +5028,7 @@
         <v>183</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5131,7 +5131,7 @@
         <v>184</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5160,7 +5160,7 @@
         <v>30</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5220,7 +5220,7 @@
         <v>79</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>82</v>
@@ -5234,7 +5234,7 @@
         <v>185</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5257,16 +5257,16 @@
         <v>77</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -5316,7 +5316,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>84</v>
@@ -5331,7 +5331,7 @@
         <v>77</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
     <row r="43">
@@ -5428,21 +5428,21 @@
         <v>84</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>121</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -5465,16 +5465,16 @@
         <v>77</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -5524,7 +5524,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>84</v>
@@ -5539,7 +5539,7 @@
         <v>77</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
     <row r="45">
@@ -5636,13 +5636,13 @@
         <v>84</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>121</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:10:14+00:00</t>
+    <t>2024-06-03T16:22:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:22:01+00:00</t>
+    <t>2024-06-03T16:23:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:23:50+00:00</t>
+    <t>2024-06-03T16:30:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:30:34+00:00</t>
+    <t>2024-06-05T12:07:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-05T12:07:44+00:00</t>
+    <t>2024-06-07T15:57:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-07T15:57:22+00:00</t>
+    <t>2024-07-01T19:46:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-01T19:46:33+00:00</t>
+    <t>2024-07-09T08:44:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T08:44:23+00:00</t>
+    <t>2024-07-10T09:54:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.1</t>
+    <t>1.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T09:54:14+00:00</t>
+    <t>2024-07-10T10:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T10:00:25+00:00</t>
+    <t>2024-07-10T10:02:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T10:02:38+00:00</t>
+    <t>2024-07-10T10:13:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T10:13:33+00:00</t>
+    <t>2024-07-10T12:01:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T12:01:49+00:00</t>
+    <t>2024-07-10T12:37:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T12:37:24+00:00</t>
+    <t>2024-07-10T13:09:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T13:09:17+00:00</t>
+    <t>2024-07-10T13:09:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T13:09:58+00:00</t>
+    <t>2024-07-10T13:27:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T13:27:13+00:00</t>
+    <t>2024-07-11T14:15:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T14:15:05+00:00</t>
+    <t>2024-07-11T14:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.0-snapshot</t>
+    <t>1.1.0-snapshot-2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T14:20:03+00:00</t>
+    <t>2024-07-11T15:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T15:32:47+00:00</t>
+    <t>2024-07-11T15:43:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T15:43:40+00:00</t>
+    <t>2024-07-11T16:04:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T16:04:15+00:00</t>
+    <t>2024-07-12T06:54:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-12T06:54:28+00:00</t>
+    <t>2024-07-12T07:24:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-27T17:01:01+00:00</t>
+    <t>2025-01-31T09:33:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-31T09:33:18+00:00</t>
+    <t>2025-02-03T16:26:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-03T16:26:04+00:00</t>
+    <t>2025-02-11T12:19:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T12:19:13+00:00</t>
+    <t>2025-02-11T12:46:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T12:46:26+00:00</t>
+    <t>2025-02-11T13:37:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T13:37:59+00:00</t>
+    <t>2025-02-11T14:09:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T14:09:44+00:00</t>
+    <t>2025-02-11T15:57:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T15:57:50+00:00</t>
+    <t>2025-02-11T16:04:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T16:04:30+00:00</t>
+    <t>2025-02-11T16:35:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-17T22:39:20+00:00</t>
+    <t>2025-02-24T08:37:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T08:37:03+00:00</t>
+    <t>2025-02-27T14:21:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T14:21:41+00:00</t>
+    <t>2025-02-27T14:23:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T14:23:05+00:00</t>
+    <t>2025-02-28T10:02:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-28T10:02:48+00:00</t>
+    <t>2025-03-05T17:59:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-05T17:59:44+00:00</t>
+    <t>2025-03-06T14:41:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T14:41:30+00:00</t>
+    <t>2025-03-06T14:56:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T14:56:25+00:00</t>
+    <t>2025-03-12T15:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-12T15:24:25+00:00</t>
+    <t>2025-03-18T14:02:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-18T14:02:39+00:00</t>
+    <t>2025-03-18T16:59:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-18T16:59:29+00:00</t>
+    <t>2025-03-21T10:50:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-snapshot-1</t>
+    <t>1.2.0-snapshot-2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T12:01:00+00:00</t>
+    <t>2026-06-19T13:53:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T13:53:04+00:00</t>
+    <t>2026-06-19T14:07:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T14:07:56+00:00</t>
+    <t>2026-06-23T09:20:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-23T09:20:47+00:00</t>
+    <t>2026-06-23T12:21:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-23T12:21:55+00:00</t>
+    <t>2026-06-26T10:36:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T10:36:05+00:00</t>
+    <t>2026-06-27T10:35:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-27T10:35:23+00:00</t>
+    <t>2026-06-30T07:59:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T07:59:11+00:00</t>
+    <t>2026-07-10T15:33:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-snapshot-2</t>
+    <t>1.2.0-snapshot-3</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T15:33:23+00:00</t>
+    <t>2026-07-10T15:46:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T15:46:03+00:00</t>
+    <t>2026-08-03T13:23:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T13:23:25+00:00</t>
+    <t>2026-08-03T14:28:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T14:28:09+00:00</t>
+    <t>2026-08-04T08:16:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/main/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T08:16:57+00:00</t>
+    <t>2026-08-04T12:10:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
